--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487114_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487114_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5994</v>
+        <v>4.1481</v>
       </c>
       <c r="E2" t="n">
-        <v>2.764</v>
+        <v>3.4392</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8354</v>
+        <v>0.7089</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4435</v>
+        <v>1.8772</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3268</v>
+        <v>1.1746</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1167</v>
+        <v>0.7026</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5631</v>
+        <v>3.0108</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2936</v>
+        <v>0.6674</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2695</v>
+        <v>2.3435</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1196</v>
+        <v>-1.1336</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0332</v>
+        <v>0.5072</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1528</v>
+        <v>-1.6408</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8157</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.868</v>
+        <v>0.4283</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0522</v>
+        <v>0.1054</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8842</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4022</v>
+        <v>3.9857</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0447</v>
+        <v>1.9628</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6425</v>
+        <v>2.0228</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3838</v>
+        <v>2.4435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0703</v>
+        <v>1.3268</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4541</v>
+        <v>1.1167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7369</v>
+        <v>2.5631</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0364</v>
+        <v>1.2936</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7733</v>
+        <v>1.2695</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1207</v>
+        <v>-0.1196</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1067</v>
+        <v>0.0332</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2274</v>
+        <v>-0.1528</v>
       </c>
       <c r="P3" t="n">
-        <v>0.965</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R3" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>1.593</v>
+        <v>1.202</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7939</v>
+        <v>1.0669</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.201</v>
+        <v>0.1352</v>
       </c>
       <c r="V3" t="n">
+        <v>1.8842</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.228</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.5138</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.999</v>
+        <v>3.1269</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6381</v>
+        <v>2.6826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3609</v>
+        <v>0.4443</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8772</v>
+        <v>3.5766</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1746</v>
+        <v>0.7991</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7026</v>
+        <v>2.7775</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0108</v>
+        <v>4.5703</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6674</v>
+        <v>1.7542</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3435</v>
+        <v>2.8161</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1336</v>
+        <v>-0.9937</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5072</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6408</v>
+        <v>-0.0386</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7371</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6153999999999999</v>
+        <v>0.5503</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3728</v>
+        <v>0.0423</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2426</v>
+        <v>0.5079</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2454</v>
+        <v>2.5544</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8814</v>
+        <v>3.1434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.364</v>
+        <v>-0.589</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5766</v>
+        <v>-0.3838</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7991</v>
+        <v>0.0703</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7775</v>
+        <v>-0.4541</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5703</v>
+        <v>0.7369</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7542</v>
+        <v>-0.0364</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8161</v>
+        <v>0.7733</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9937</v>
+        <v>-1.1207</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.1067</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0386</v>
+        <v>-1.2274</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3312</v>
+        <v>0.7453</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7588</v>
+        <v>0.8927</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4276</v>
+        <v>-0.1474</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2105</v>
+        <v>2.446</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3286</v>
+        <v>2.2688</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1181</v>
+        <v>0.1772</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6046</v>
+        <v>2.556</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1469</v>
+        <v>-1.5938</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7515</v>
+        <v>4.1499</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7854</v>
+        <v>3.1235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7347</v>
+        <v>-0.2381</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0507</v>
+        <v>3.3616</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1808</v>
+        <v>-0.5674</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8817</v>
+        <v>-1.3557</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2992</v>
+        <v>0.7883</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2432</v>
+        <v>-0.2029</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1057</v>
+        <v>-0.1755</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1375</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1723</v>
+        <v>2.4247</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9684</v>
+        <v>2.3286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2039</v>
+        <v>0.0961</v>
       </c>
       <c r="G7" t="n">
-        <v>2.556</v>
+        <v>1.6046</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5938</v>
+        <v>-0.1469</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1499</v>
+        <v>1.7515</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1235</v>
+        <v>2.7854</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2381</v>
+        <v>0.7347</v>
       </c>
       <c r="L7" t="n">
-        <v>3.3616</v>
+        <v>2.0507</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5674</v>
+        <v>-1.1808</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3557</v>
+        <v>-0.8817</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7883</v>
+        <v>-0.2992</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4766</v>
+        <v>-0.0291</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4759</v>
+        <v>-0.1057</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0007</v>
+        <v>0.0766</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2859</v>
+        <v>0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4649</v>
+        <v>0.787</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8011</v>
+        <v>1.6364</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2659</v>
+        <v>-0.8494</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.475</v>
+        <v>1.9105</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.423</v>
+        <v>1.8493</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2353</v>
+        <v>2.9712</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3674</v>
+        <v>1.4903</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6026</v>
+        <v>1.4809</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2397</v>
+        <v>-1.0607</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5807</v>
+        <v>-1.4292</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8204</v>
+        <v>0.3684</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0906</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3993</v>
+        <v>0.5952</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6914</v>
+        <v>0.3741</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6562</v>
+        <v>-1.5138</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6562</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.214</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.39</v>
+        <v>-1.0013</v>
       </c>
       <c r="F9" t="n">
-        <v>2.604</v>
+        <v>1.7841</v>
       </c>
       <c r="G9" t="n">
-        <v>1.521</v>
+        <v>-0.475</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.179</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7001</v>
+        <v>-1.423</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8343</v>
+        <v>-0.2353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7761</v>
+        <v>0.3674</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0582</v>
+        <v>-0.6026</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3132</v>
+        <v>-0.2397</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9550999999999999</v>
+        <v>0.5807</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6419</v>
+        <v>-0.8204</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3161</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2949</v>
+        <v>0.4085</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6359</v>
+        <v>0.199</v>
       </c>
       <c r="U9" t="n">
-        <v>1.659</v>
+        <v>0.2095</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.673</v>
+        <v>0.5189</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7365</v>
+        <v>0.008</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0636</v>
+        <v>0.5109</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9105</v>
+        <v>0.4151</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0612</v>
+        <v>-0.4574</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8493</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9712</v>
+        <v>0.7219</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4903</v>
+        <v>-0.5641</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4809</v>
+        <v>1.286</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0607</v>
+        <v>-0.3067</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4292</v>
+        <v>0.1067</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3684</v>
+        <v>-0.4134</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.579</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.1038</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6954</v>
+        <v>0.2512</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1599</v>
+        <v>-0.1474</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4372</v>
+        <v>0.464</v>
       </c>
       <c r="E11" t="n">
         <v>0.2859</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1514</v>
+        <v>0.1781</v>
       </c>
       <c r="G11" t="n">
         <v>0.1335</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V11" t="n">
         <v>0.2859</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0648</v>
+        <v>0.0639</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3926</v>
+        <v>-1.7905</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4573</v>
+        <v>1.8544</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4151</v>
+        <v>1.521</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4574</v>
+        <v>-0.179</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.7001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7219</v>
+        <v>1.8343</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5641</v>
+        <v>0.7761</v>
       </c>
       <c r="L12" t="n">
-        <v>1.286</v>
+        <v>1.0582</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3067</v>
+        <v>-0.3132</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1067</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4134</v>
+        <v>0.6419</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R12" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3503</v>
+        <v>1.1448</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1494</v>
+        <v>0.2353</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.201</v>
+        <v>0.9095</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.273</v>
+        <v>-0.0925</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7271</v>
+        <v>-0.627</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4541</v>
+        <v>0.5344</v>
       </c>
       <c r="G13" t="n">
         <v>-0.267</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0059</v>
+        <v>0.1745</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0535</v>
+        <v>0.1338</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.2097</v>
+        <v>21.2099</v>
       </c>
       <c r="E14" t="n">
-        <v>14.3368</v>
+        <v>14.3369</v>
       </c>
       <c r="F14" t="n">
-        <v>6.872699999999999</v>
+        <v>6.8728</v>
       </c>
       <c r="G14" t="n">
         <v>14.9122</v>
       </c>
       <c r="H14" t="n">
-        <v>2.003</v>
+        <v>2.003000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>12.9095</v>
@@ -1528,7 +1528,7 @@
         <v>15.1696</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.502</v>
+        <v>-6.502000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-4.2423</v>
@@ -1546,13 +1546,13 @@
         <v>12.5455</v>
       </c>
       <c r="S14" t="n">
-        <v>5.644700000000001</v>
+        <v>5.6449</v>
       </c>
       <c r="T14" t="n">
-        <v>3.470400000000001</v>
+        <v>3.4704</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1742</v>
+        <v>2.1743</v>
       </c>
       <c r="V14" t="n">
         <v>2.5827</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5588</v>
+        <v>3.1005</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6208</v>
+        <v>4.5206</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.062</v>
+        <v>-1.4202</v>
       </c>
       <c r="G15" t="n">
         <v>4.2503</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1329</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0556</v>
+        <v>-0.0446</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1885</v>
+        <v>-0.5467</v>
       </c>
       <c r="V15" t="n">
         <v>1.7575</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2409</v>
+        <v>1.8153</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9298</v>
+        <v>1.1301</v>
       </c>
       <c r="F16" t="n">
-        <v>0.311</v>
+        <v>0.6851</v>
       </c>
       <c r="G16" t="n">
         <v>1.4814</v>
@@ -1702,13 +1702,13 @@
         <v>0.193</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4336</v>
+        <v>0.1408</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1044</v>
+        <v>0.0959</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3292</v>
+        <v>0.0449</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.46</v>
+        <v>-0.2558</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7271</v>
+        <v>1.2148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.267</v>
+        <v>-1.4707</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4006</v>
+        <v>0.2156</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.7854</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4006</v>
+        <v>1.0011</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6676</v>
+        <v>1.93</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6676</v>
+        <v>1.8472</v>
       </c>
       <c r="M17" t="n">
-        <v>0.267</v>
+        <v>-1.7144</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.8682</v>
       </c>
       <c r="O17" t="n">
-        <v>0.267</v>
+        <v>-0.8461</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0595</v>
+        <v>-0.7876</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0595</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. KIAMESO</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9405</v>
+        <v>-0.46</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8461</v>
+        <v>-0.7271</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0944</v>
+        <v>0.267</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.881</v>
+        <v>-0.4006</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.14</v>
+        <v>-0.4006</v>
       </c>
       <c r="J18" t="n">
         <v>-0.6676</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>-0.6676</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>-0.2134</v>
+        <v>0.267</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0735</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.14</v>
+        <v>0.267</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4455</v>
+        <v>-0.0595</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.267</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>N. KIAMESO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1373</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8143</v>
+        <v>-0.8461</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9515</v>
+        <v>0.0391</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2156</v>
+        <v>-0.881</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7854</v>
+        <v>-0.7411</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0011</v>
+        <v>-0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>1.93</v>
+        <v>-0.6676</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0828</v>
+        <v>-0.6676</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8472</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7144</v>
+        <v>-0.2134</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8682</v>
+        <v>-0.0735</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8461</v>
+        <v>-0.14</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.669</v>
+        <v>-0.312</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1157</v>
+        <v>-0.1785</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5533</v>
+        <v>-0.1335</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.31</v>
+        <v>-2.4348</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2946</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0154</v>
+        <v>-1.6409</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8435</v>
@@ -2014,13 +2014,13 @@
         <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7404</v>
+        <v>-0.8652</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9967</v>
+        <v>-0.496</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7436</v>
+        <v>-0.3692</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6562</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4217</v>
+        <v>-5.8986</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1128</v>
+        <v>-3.2144</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3089</v>
+        <v>-2.6843</v>
       </c>
       <c r="G21" t="n">
         <v>-5.4906</v>
@@ -2092,13 +2092,13 @@
         <v>2.8951</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7252</v>
+        <v>0.2482</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2123</v>
+        <v>0.1108</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5129</v>
+        <v>0.1374</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6562</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2485</v>
+        <v>-6.6894</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5278</v>
+        <v>-3.1286</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7207</v>
+        <v>-3.5607</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3804</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2247</v>
+        <v>-0.2161</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5447</v>
+        <v>-0.0561</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5138</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.491300000000001</v>
+        <v>-7.5768</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7293</v>
+        <v>-5.0283</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.762</v>
+        <v>-2.5485</v>
       </c>
       <c r="G23" t="n">
         <v>-6.8637</v>
@@ -2248,13 +2248,13 @@
         <v>2.7021</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1138</v>
+        <v>-1.1994</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5321</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5817</v>
+        <v>-0.3682</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2859</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-21.2096</v>
+        <v>-19.2066</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8728</v>
+        <v>-6.8729</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.3369</v>
+        <v>-12.3341</v>
       </c>
       <c r="G24" t="n">
         <v>-14.9125</v>
@@ -2311,7 +2311,7 @@
         <v>-21.4146</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.244999999999999</v>
+        <v>-6.245</v>
       </c>
       <c r="O24" t="n">
         <v>-15.1696</v>
@@ -2326,16 +2326,16 @@
         <v>14.4756</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.6448</v>
+        <v>-3.641999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>-2.1743</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.4704</v>
+        <v>-1.4677</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.582599999999999</v>
+        <v>-2.5826</v>
       </c>
       <c r="W24" t="n">
         <v>1.3449</v>
